--- a/data_lake/industry/TrendForce/PV.xlsx
+++ b/data_lake/industry/TrendForce/PV.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E2C2781-2C27-604B-8747-D9C0DE20A896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C76467-D26F-B242-B37F-07FCC07CB2B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16680" yWindow="780" windowWidth="19320" windowHeight="20760" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16680" yWindow="780" windowWidth="19320" windowHeight="20760" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -497,6 +497,9 @@
                 <c:pt idx="30">
                   <c:v>46267</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>46274</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -737,6 +740,9 @@
                 <c:pt idx="30">
                   <c:v>46267</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>46274</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -977,6 +983,9 @@
                 <c:pt idx="30">
                   <c:v>46267</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>46274</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1216,6 +1225,9 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>46267</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46274</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1679,6 +1691,9 @@
                 <c:pt idx="30">
                   <c:v>46267</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>46274</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1919,6 +1934,9 @@
                 <c:pt idx="30">
                   <c:v>46267</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>46274</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2158,6 +2176,9 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>46267</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46274</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2622,6 +2643,9 @@
                 <c:pt idx="30">
                   <c:v>46267</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>46274</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2799,6 +2823,9 @@
                 <c:pt idx="30">
                   <c:v>46267</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>46274</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2975,6 +3002,9 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>46267</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46274</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3440,6 +3470,9 @@
                 <c:pt idx="30">
                   <c:v>46267</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>46274</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3679,6 +3712,9 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>46267</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46274</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4142,6 +4178,9 @@
                 <c:pt idx="30">
                   <c:v>46267</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>46274</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4382,6 +4421,9 @@
                 <c:pt idx="30">
                   <c:v>46267</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>46274</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4621,6 +4663,9 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>46267</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46274</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8175,7 +8220,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U33"/>
+  <dimension ref="A1:U34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.5" style="7" bestFit="1" customWidth="1"/>
@@ -9845,6 +9890,20 @@
         <v>17.5</v>
       </c>
     </row>
+    <row r="34" spans="1:16">
+      <c r="A34" s="7">
+        <v>46274</v>
+      </c>
+      <c r="B34" s="7">
+        <v>46274</v>
+      </c>
+      <c r="C34" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
@@ -9860,7 +9919,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U33"/>
+  <dimension ref="A1:U34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.1640625" style="7" bestFit="1" customWidth="1"/>
@@ -11241,6 +11300,20 @@
       </c>
       <c r="M33" s="10">
         <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="7">
+        <v>46274</v>
+      </c>
+      <c r="B34" s="7">
+        <v>46274</v>
+      </c>
+      <c r="C34" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -11257,7 +11330,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U33"/>
+  <dimension ref="A1:U34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.83203125" style="7" bestFit="1" customWidth="1"/>
@@ -12638,6 +12711,20 @@
       </c>
       <c r="M33" s="10">
         <v>0.31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="7">
+        <v>46274</v>
+      </c>
+      <c r="B34" s="7">
+        <v>46274</v>
+      </c>
+      <c r="C34" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -12654,7 +12741,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U33"/>
+  <dimension ref="A1:U34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="7" bestFit="1" customWidth="1"/>
@@ -13750,6 +13837,20 @@
       </c>
       <c r="J33" s="10">
         <v>0.7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="7">
+        <v>46274</v>
+      </c>
+      <c r="B34" s="7">
+        <v>46274</v>
+      </c>
+      <c r="C34" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -13766,7 +13867,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U33"/>
+  <dimension ref="A1:U34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="7" bestFit="1" customWidth="1"/>
@@ -15149,6 +15250,20 @@
       </c>
       <c r="M33" s="14">
         <v>8.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="7">
+        <v>46274</v>
+      </c>
+      <c r="B34" s="7">
+        <v>46274</v>
+      </c>
+      <c r="C34" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/industry/TrendForce/PV.xlsx
+++ b/data_lake/industry/TrendForce/PV.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C76467-D26F-B242-B37F-07FCC07CB2B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCEB772B-D4DA-1045-A1D0-C549644960C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16680" yWindow="780" windowWidth="19320" windowHeight="20760" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16680" yWindow="780" windowWidth="19320" windowHeight="20760" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -602,6 +602,9 @@
                 <c:pt idx="30">
                   <c:v>33.5</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>33.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -845,6 +848,9 @@
                 <c:pt idx="30">
                   <c:v>32.5</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>32.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1088,6 +1094,9 @@
                 <c:pt idx="30">
                   <c:v>31</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>31</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1329,6 +1338,9 @@
                   <c:v>17.5</c:v>
                 </c:pt>
                 <c:pt idx="30">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="31">
                   <c:v>17.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1796,6 +1808,9 @@
                 <c:pt idx="30">
                   <c:v>1.08</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>1.02</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2039,6 +2054,9 @@
                 <c:pt idx="30">
                   <c:v>1.17</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>1.1200000000000001</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2281,6 +2299,9 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1.02</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3107,6 +3128,9 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>0.31</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3575,6 +3599,9 @@
                 <c:pt idx="30">
                   <c:v>0.7</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.7</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3816,6 +3843,9 @@
                   <c:v>0.7</c:v>
                 </c:pt>
                 <c:pt idx="30">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="31">
                   <c:v>0.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -4283,6 +4313,9 @@
                 <c:pt idx="30">
                   <c:v>10.5</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>10.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4526,6 +4559,9 @@
                 <c:pt idx="30">
                   <c:v>17</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>17</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4767,6 +4803,9 @@
                   <c:v>8.5</c:v>
                 </c:pt>
                 <c:pt idx="30">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="31">
                   <c:v>8.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -9903,6 +9942,42 @@
       <c r="D34" s="9" t="s">
         <v>40</v>
       </c>
+      <c r="E34" s="13">
+        <v>45</v>
+      </c>
+      <c r="F34" s="13">
+        <v>33</v>
+      </c>
+      <c r="G34" s="13">
+        <v>33.5</v>
+      </c>
+      <c r="H34" s="13">
+        <v>43</v>
+      </c>
+      <c r="I34" s="13">
+        <v>32</v>
+      </c>
+      <c r="J34" s="13">
+        <v>32.5</v>
+      </c>
+      <c r="K34" s="13">
+        <v>41</v>
+      </c>
+      <c r="L34" s="13">
+        <v>30</v>
+      </c>
+      <c r="M34" s="13">
+        <v>31</v>
+      </c>
+      <c r="N34" s="13">
+        <v>22</v>
+      </c>
+      <c r="O34" s="14">
+        <v>13.1</v>
+      </c>
+      <c r="P34" s="14">
+        <v>17.5</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -11315,6 +11390,33 @@
       <c r="D34" s="9" t="s">
         <v>40</v>
       </c>
+      <c r="E34" s="10">
+        <v>1.05</v>
+      </c>
+      <c r="F34" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G34" s="10">
+        <v>1.02</v>
+      </c>
+      <c r="H34" s="10">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="I34" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J34" s="10">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="K34" s="10">
+        <v>1.05</v>
+      </c>
+      <c r="L34" s="10">
+        <v>1</v>
+      </c>
+      <c r="M34" s="10">
+        <v>1.02</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -12726,6 +12828,33 @@
       <c r="D34" s="9" t="s">
         <v>40</v>
       </c>
+      <c r="E34" s="10">
+        <v>0.31</v>
+      </c>
+      <c r="F34" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="G34" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="H34" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="I34" s="10">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="J34" s="10">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="K34" s="10">
+        <v>0.31</v>
+      </c>
+      <c r="L34" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="M34" s="10">
+        <v>0.3</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -13851,6 +13980,24 @@
       </c>
       <c r="D34" s="9" t="s">
         <v>40</v>
+      </c>
+      <c r="E34" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="F34" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="G34" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="H34" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="I34" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="J34" s="10">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -15264,6 +15411,33 @@
       </c>
       <c r="D34" s="9" t="s">
         <v>40</v>
+      </c>
+      <c r="E34" s="14">
+        <v>11</v>
+      </c>
+      <c r="F34" s="14">
+        <v>10</v>
+      </c>
+      <c r="G34" s="14">
+        <v>10.5</v>
+      </c>
+      <c r="H34" s="14">
+        <v>17.5</v>
+      </c>
+      <c r="I34" s="14">
+        <v>17</v>
+      </c>
+      <c r="J34" s="14">
+        <v>17</v>
+      </c>
+      <c r="K34" s="14">
+        <v>9</v>
+      </c>
+      <c r="L34" s="14">
+        <v>8</v>
+      </c>
+      <c r="M34" s="14">
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/industry/TrendForce/PV.xlsx
+++ b/data_lake/industry/TrendForce/PV.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCEB772B-D4DA-1045-A1D0-C549644960C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D4A9D1-B625-2F41-9CB1-A047548EC896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16680" yWindow="780" windowWidth="19320" windowHeight="20760" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16680" yWindow="780" windowWidth="19320" windowHeight="20760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -500,6 +500,9 @@
                 <c:pt idx="31">
                   <c:v>46274</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46281</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -603,6 +606,9 @@
                   <c:v>33.5</c:v>
                 </c:pt>
                 <c:pt idx="31">
+                  <c:v>33.5</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>33.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -746,6 +752,9 @@
                 <c:pt idx="31">
                   <c:v>46274</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46281</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -849,6 +858,9 @@
                   <c:v>32.5</c:v>
                 </c:pt>
                 <c:pt idx="31">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>32.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -992,6 +1004,9 @@
                 <c:pt idx="31">
                   <c:v>46274</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46281</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1095,6 +1110,9 @@
                   <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="31">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>31</c:v>
                 </c:pt>
               </c:numCache>
@@ -1238,6 +1256,9 @@
                 <c:pt idx="31">
                   <c:v>46274</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46281</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1341,6 +1362,9 @@
                   <c:v>17.5</c:v>
                 </c:pt>
                 <c:pt idx="31">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>17.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1706,6 +1730,9 @@
                 <c:pt idx="31">
                   <c:v>46274</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46281</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1810,6 +1837,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>1.02</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1952,6 +1982,9 @@
                 <c:pt idx="31">
                   <c:v>46274</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46281</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2056,6 +2089,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>1.1200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1.1000000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2198,6 +2234,9 @@
                 <c:pt idx="31">
                   <c:v>46274</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46281</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2301,6 +2340,9 @@
                   <c:v>1.1000000000000001</c:v>
                 </c:pt>
                 <c:pt idx="31">
+                  <c:v>1.02</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>1.02</c:v>
                 </c:pt>
               </c:numCache>
@@ -2667,6 +2709,9 @@
                 <c:pt idx="31">
                   <c:v>46274</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46281</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2847,6 +2892,9 @@
                 <c:pt idx="31">
                   <c:v>46274</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46281</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3027,6 +3075,9 @@
                 <c:pt idx="31">
                   <c:v>46274</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46281</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3131,6 +3182,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.31</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3497,6 +3551,9 @@
                 <c:pt idx="31">
                   <c:v>46274</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46281</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3600,6 +3657,9 @@
                   <c:v>0.7</c:v>
                 </c:pt>
                 <c:pt idx="31">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>0.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -3743,6 +3803,9 @@
                 <c:pt idx="31">
                   <c:v>46274</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46281</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3846,6 +3909,9 @@
                   <c:v>0.7</c:v>
                 </c:pt>
                 <c:pt idx="31">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>0.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -4211,6 +4277,9 @@
                 <c:pt idx="31">
                   <c:v>46274</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46281</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4314,6 +4383,9 @@
                   <c:v>10.5</c:v>
                 </c:pt>
                 <c:pt idx="31">
+                  <c:v>10.5</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>10.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -4457,6 +4529,9 @@
                 <c:pt idx="31">
                   <c:v>46274</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46281</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4560,6 +4635,9 @@
                   <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="31">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>17</c:v>
                 </c:pt>
               </c:numCache>
@@ -4703,6 +4781,9 @@
                 <c:pt idx="31">
                   <c:v>46274</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46281</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4806,6 +4887,9 @@
                   <c:v>8.5</c:v>
                 </c:pt>
                 <c:pt idx="31">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>8.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -8259,7 +8343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U34"/>
+  <dimension ref="A1:U35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.5" style="7" bestFit="1" customWidth="1"/>
@@ -9979,6 +10063,56 @@
         <v>17.5</v>
       </c>
     </row>
+    <row r="35" spans="1:16">
+      <c r="A35" s="7">
+        <v>46281</v>
+      </c>
+      <c r="B35" s="7">
+        <v>46281</v>
+      </c>
+      <c r="C35" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E35" s="13">
+        <v>45</v>
+      </c>
+      <c r="F35" s="13">
+        <v>33</v>
+      </c>
+      <c r="G35" s="13">
+        <v>33.5</v>
+      </c>
+      <c r="H35" s="13">
+        <v>43</v>
+      </c>
+      <c r="I35" s="13">
+        <v>32</v>
+      </c>
+      <c r="J35" s="13">
+        <v>32.5</v>
+      </c>
+      <c r="K35" s="13">
+        <v>41</v>
+      </c>
+      <c r="L35" s="13">
+        <v>30</v>
+      </c>
+      <c r="M35" s="13">
+        <v>31</v>
+      </c>
+      <c r="N35" s="13">
+        <v>22</v>
+      </c>
+      <c r="O35" s="14">
+        <v>13.1</v>
+      </c>
+      <c r="P35" s="14">
+        <v>17.5</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
@@ -9994,7 +10128,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U34"/>
+  <dimension ref="A1:U35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.1640625" style="7" bestFit="1" customWidth="1"/>
@@ -11415,6 +11549,47 @@
         <v>1</v>
       </c>
       <c r="M34" s="10">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="7">
+        <v>46281</v>
+      </c>
+      <c r="B35" s="7">
+        <v>46281</v>
+      </c>
+      <c r="C35" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E35" s="10">
+        <v>1.02</v>
+      </c>
+      <c r="F35" s="10">
+        <v>0.98</v>
+      </c>
+      <c r="G35" s="10">
+        <v>1</v>
+      </c>
+      <c r="H35" s="10">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="I35" s="10">
+        <v>1.08</v>
+      </c>
+      <c r="J35" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="K35" s="10">
+        <v>1.05</v>
+      </c>
+      <c r="L35" s="10">
+        <v>1</v>
+      </c>
+      <c r="M35" s="10">
         <v>1.02</v>
       </c>
     </row>
@@ -11432,7 +11607,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U34"/>
+  <dimension ref="A1:U35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.83203125" style="7" bestFit="1" customWidth="1"/>
@@ -12854,6 +13029,47 @@
       </c>
       <c r="M34" s="10">
         <v>0.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="7">
+        <v>46281</v>
+      </c>
+      <c r="B35" s="7">
+        <v>46281</v>
+      </c>
+      <c r="C35" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E35" s="10">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="F35" s="10">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G35" s="10">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="H35" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="I35" s="10">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J35" s="10">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="K35" s="10">
+        <v>0.32</v>
+      </c>
+      <c r="L35" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="M35" s="10">
+        <v>0.31</v>
       </c>
     </row>
   </sheetData>
@@ -12870,7 +13086,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U34"/>
+  <dimension ref="A1:U35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="7" bestFit="1" customWidth="1"/>
@@ -13997,6 +14213,38 @@
         <v>0.7</v>
       </c>
       <c r="J34" s="10">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="7">
+        <v>46281</v>
+      </c>
+      <c r="B35" s="7">
+        <v>46281</v>
+      </c>
+      <c r="C35" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E35" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="F35" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="G35" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="H35" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="I35" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="J35" s="10">
         <v>0.7</v>
       </c>
     </row>
@@ -14014,7 +14262,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U34"/>
+  <dimension ref="A1:U35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="7" bestFit="1" customWidth="1"/>
@@ -15437,6 +15685,47 @@
         <v>8</v>
       </c>
       <c r="M34" s="14">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="7">
+        <v>46281</v>
+      </c>
+      <c r="B35" s="7">
+        <v>46281</v>
+      </c>
+      <c r="C35" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E35" s="14">
+        <v>11</v>
+      </c>
+      <c r="F35" s="14">
+        <v>10</v>
+      </c>
+      <c r="G35" s="14">
+        <v>10.5</v>
+      </c>
+      <c r="H35" s="14">
+        <v>17.5</v>
+      </c>
+      <c r="I35" s="14">
+        <v>17</v>
+      </c>
+      <c r="J35" s="14">
+        <v>17</v>
+      </c>
+      <c r="K35" s="14">
+        <v>9</v>
+      </c>
+      <c r="L35" s="14">
+        <v>8</v>
+      </c>
+      <c r="M35" s="14">
         <v>8.5</v>
       </c>
     </row>

--- a/data_lake/industry/TrendForce/PV.xlsx
+++ b/data_lake/industry/TrendForce/PV.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D4A9D1-B625-2F41-9CB1-A047548EC896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49FF5528-EAEE-AC46-8C47-C33F8A4797C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16680" yWindow="780" windowWidth="19320" windowHeight="20760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18020" yWindow="780" windowWidth="17980" windowHeight="20700" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -503,6 +503,9 @@
                 <c:pt idx="32">
                   <c:v>46281</c:v>
                 </c:pt>
+                <c:pt idx="33">
+                  <c:v>46288</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -609,6 +612,9 @@
                   <c:v>33.5</c:v>
                 </c:pt>
                 <c:pt idx="32">
+                  <c:v>33.5</c:v>
+                </c:pt>
+                <c:pt idx="33">
                   <c:v>33.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -755,6 +761,9 @@
                 <c:pt idx="32">
                   <c:v>46281</c:v>
                 </c:pt>
+                <c:pt idx="33">
+                  <c:v>46288</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -861,6 +870,9 @@
                   <c:v>32.5</c:v>
                 </c:pt>
                 <c:pt idx="32">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="33">
                   <c:v>32.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1007,6 +1019,9 @@
                 <c:pt idx="32">
                   <c:v>46281</c:v>
                 </c:pt>
+                <c:pt idx="33">
+                  <c:v>46288</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1113,6 +1128,9 @@
                   <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="32">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="33">
                   <c:v>31</c:v>
                 </c:pt>
               </c:numCache>
@@ -1259,6 +1277,9 @@
                 <c:pt idx="32">
                   <c:v>46281</c:v>
                 </c:pt>
+                <c:pt idx="33">
+                  <c:v>46288</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1365,6 +1386,9 @@
                   <c:v>17.5</c:v>
                 </c:pt>
                 <c:pt idx="32">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="33">
                   <c:v>17.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1733,6 +1757,9 @@
                 <c:pt idx="32">
                   <c:v>46281</c:v>
                 </c:pt>
+                <c:pt idx="33">
+                  <c:v>46288</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1839,6 +1866,9 @@
                   <c:v>1.02</c:v>
                 </c:pt>
                 <c:pt idx="32">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="33">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -1985,6 +2015,9 @@
                 <c:pt idx="32">
                   <c:v>46281</c:v>
                 </c:pt>
+                <c:pt idx="33">
+                  <c:v>46288</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2092,6 +2125,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1.1299999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2237,6 +2273,9 @@
                 <c:pt idx="32">
                   <c:v>46281</c:v>
                 </c:pt>
+                <c:pt idx="33">
+                  <c:v>46288</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2343,6 +2382,9 @@
                   <c:v>1.02</c:v>
                 </c:pt>
                 <c:pt idx="32">
+                  <c:v>1.02</c:v>
+                </c:pt>
+                <c:pt idx="33">
                   <c:v>1.02</c:v>
                 </c:pt>
               </c:numCache>
@@ -2712,6 +2754,9 @@
                 <c:pt idx="32">
                   <c:v>46281</c:v>
                 </c:pt>
+                <c:pt idx="33">
+                  <c:v>46288</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2895,6 +2940,9 @@
                 <c:pt idx="32">
                   <c:v>46281</c:v>
                 </c:pt>
+                <c:pt idx="33">
+                  <c:v>46288</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3078,6 +3126,9 @@
                 <c:pt idx="32">
                   <c:v>46281</c:v>
                 </c:pt>
+                <c:pt idx="33">
+                  <c:v>46288</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3185,6 +3236,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>0.31</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.32</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3554,6 +3608,9 @@
                 <c:pt idx="32">
                   <c:v>46281</c:v>
                 </c:pt>
+                <c:pt idx="33">
+                  <c:v>46288</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3660,6 +3717,9 @@
                   <c:v>0.7</c:v>
                 </c:pt>
                 <c:pt idx="32">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="33">
                   <c:v>0.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -3806,6 +3866,9 @@
                 <c:pt idx="32">
                   <c:v>46281</c:v>
                 </c:pt>
+                <c:pt idx="33">
+                  <c:v>46288</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3912,6 +3975,9 @@
                   <c:v>0.7</c:v>
                 </c:pt>
                 <c:pt idx="32">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="33">
                   <c:v>0.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -4280,6 +4346,9 @@
                 <c:pt idx="32">
                   <c:v>46281</c:v>
                 </c:pt>
+                <c:pt idx="33">
+                  <c:v>46288</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4386,6 +4455,9 @@
                   <c:v>10.5</c:v>
                 </c:pt>
                 <c:pt idx="32">
+                  <c:v>10.5</c:v>
+                </c:pt>
+                <c:pt idx="33">
                   <c:v>10.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -4532,6 +4604,9 @@
                 <c:pt idx="32">
                   <c:v>46281</c:v>
                 </c:pt>
+                <c:pt idx="33">
+                  <c:v>46288</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4638,6 +4713,9 @@
                   <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="32">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="33">
                   <c:v>17</c:v>
                 </c:pt>
               </c:numCache>
@@ -4784,6 +4862,9 @@
                 <c:pt idx="32">
                   <c:v>46281</c:v>
                 </c:pt>
+                <c:pt idx="33">
+                  <c:v>46288</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4890,6 +4971,9 @@
                   <c:v>8.5</c:v>
                 </c:pt>
                 <c:pt idx="32">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="33">
                   <c:v>8.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -8343,7 +8427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U35"/>
+  <dimension ref="A1:U36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.5" style="7" bestFit="1" customWidth="1"/>
@@ -10113,6 +10197,56 @@
         <v>17.5</v>
       </c>
     </row>
+    <row r="36" spans="1:16">
+      <c r="A36" s="7">
+        <v>46288</v>
+      </c>
+      <c r="B36" s="7">
+        <v>46288</v>
+      </c>
+      <c r="C36" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E36" s="13">
+        <v>45</v>
+      </c>
+      <c r="F36" s="13">
+        <v>33</v>
+      </c>
+      <c r="G36" s="13">
+        <v>33.5</v>
+      </c>
+      <c r="H36" s="13">
+        <v>43</v>
+      </c>
+      <c r="I36" s="13">
+        <v>32</v>
+      </c>
+      <c r="J36" s="13">
+        <v>32.5</v>
+      </c>
+      <c r="K36" s="13">
+        <v>41</v>
+      </c>
+      <c r="L36" s="13">
+        <v>30</v>
+      </c>
+      <c r="M36" s="13">
+        <v>31</v>
+      </c>
+      <c r="N36" s="13">
+        <v>22</v>
+      </c>
+      <c r="O36" s="14">
+        <v>13.1</v>
+      </c>
+      <c r="P36" s="14">
+        <v>17.5</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
@@ -10128,7 +10262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U35"/>
+  <dimension ref="A1:U36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.1640625" style="7" bestFit="1" customWidth="1"/>
@@ -11590,6 +11724,47 @@
         <v>1</v>
       </c>
       <c r="M35" s="10">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" s="7">
+        <v>46288</v>
+      </c>
+      <c r="B36" s="7">
+        <v>46288</v>
+      </c>
+      <c r="C36" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E36" s="10">
+        <v>1</v>
+      </c>
+      <c r="F36" s="10">
+        <v>0.95</v>
+      </c>
+      <c r="G36" s="10">
+        <v>1</v>
+      </c>
+      <c r="H36" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="I36" s="10">
+        <v>1.08</v>
+      </c>
+      <c r="J36" s="10">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="K36" s="10">
+        <v>1.05</v>
+      </c>
+      <c r="L36" s="10">
+        <v>1</v>
+      </c>
+      <c r="M36" s="10">
         <v>1.02</v>
       </c>
     </row>
@@ -11607,7 +11782,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U35"/>
+  <dimension ref="A1:U36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.83203125" style="7" bestFit="1" customWidth="1"/>
@@ -13070,6 +13245,47 @@
       </c>
       <c r="M35" s="10">
         <v>0.31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" s="7">
+        <v>46288</v>
+      </c>
+      <c r="B36" s="7">
+        <v>46288</v>
+      </c>
+      <c r="C36" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E36" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="F36" s="10">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="G36" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="H36" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="I36" s="10">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="J36" s="10">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="K36" s="10">
+        <v>0.32</v>
+      </c>
+      <c r="L36" s="10">
+        <v>0.31</v>
+      </c>
+      <c r="M36" s="10">
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -13086,7 +13302,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U35"/>
+  <dimension ref="A1:U36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="7" bestFit="1" customWidth="1"/>
@@ -14245,6 +14461,38 @@
         <v>0.7</v>
       </c>
       <c r="J35" s="10">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="7">
+        <v>46288</v>
+      </c>
+      <c r="B36" s="7">
+        <v>46288</v>
+      </c>
+      <c r="C36" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E36" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="F36" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="G36" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="H36" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="I36" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="J36" s="10">
         <v>0.7</v>
       </c>
     </row>
@@ -14262,7 +14510,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U35"/>
+  <dimension ref="A1:U36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="7" bestFit="1" customWidth="1"/>
@@ -15726,6 +15974,47 @@
         <v>8</v>
       </c>
       <c r="M35" s="14">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" s="7">
+        <v>46288</v>
+      </c>
+      <c r="B36" s="7">
+        <v>46288</v>
+      </c>
+      <c r="C36" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E36" s="14">
+        <v>11</v>
+      </c>
+      <c r="F36" s="14">
+        <v>10</v>
+      </c>
+      <c r="G36" s="14">
+        <v>10.5</v>
+      </c>
+      <c r="H36" s="14">
+        <v>17.5</v>
+      </c>
+      <c r="I36" s="14">
+        <v>17</v>
+      </c>
+      <c r="J36" s="14">
+        <v>17</v>
+      </c>
+      <c r="K36" s="14">
+        <v>9</v>
+      </c>
+      <c r="L36" s="14">
+        <v>8</v>
+      </c>
+      <c r="M36" s="14">
         <v>8.5</v>
       </c>
     </row>
